--- a/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_r2/post_rank_positive_return_rsi_bias_filter/staggered_7d/rsi_7_gt_60__bias_15_gt_-0.02/next_day_vwap/next_day_vwap_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_r2/post_rank_positive_return_rsi_bias_filter/staggered_7d/rsi_7_gt_60__bias_15_gt_-0.02/next_day_vwap/next_day_vwap_annual_metrics.xlsx
@@ -471,13 +471,13 @@
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -560,43 +560,43 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>-0.04789445737530518</v>
+        <v>0.04019571119698995</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>-0.02176047699359285</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>-0.02671531845431496</v>
+        <v>0.06333437438734091</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.3102881551755391</v>
+        <v>0.243585286192227</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2799201080287301</v>
+        <v>0.2133188844915984</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-0.07217037726014548</v>
+        <v>0.2429896634181241</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.1024959641971843</v>
+        <v>0.3478406416891481</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0.00435266260566698</v>
+        <v>0.3881546535739639</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.2156703053716708</v>
+        <v>0.1780505146516361</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.1506490308477421</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.2127064592755743</v>
+        <v>0.1307537979417097</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>-0.2501593319080614</v>
+        <v>0.2557718876385517</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>24.97570546788144</v>
+        <v>18.67010033478667</v>
       </c>
     </row>
     <row r="3">
@@ -606,43 +606,43 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.2068990657632136</v>
+        <v>-0.1065702109520901</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>-0.2255774308756096</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.02411908673260443</v>
+        <v>0.1536721999955126</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.2363811373931042</v>
+        <v>0.167508566734918</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.2147445781752048</v>
+        <v>0.1663819230219392</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.9660603616272734</v>
+        <v>-0.7058908971028687</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-1.330542584471176</v>
+        <v>-0.9830068226522815</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0.1439630913224235</v>
+        <v>0.8476339579700458</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.2525329372260122</v>
+        <v>0.1495554488597143</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>0.2845881262232945</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.1638087575088237</v>
+        <v>0.09881169412402613</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>-0.8492344949197523</v>
+        <v>-0.7403327986897263</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>21.39292496332405</v>
+        <v>15.99836134352879</v>
       </c>
     </row>
     <row r="4">
@@ -652,43 +652,43 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.1320476829650913</v>
+        <v>-0.1290537841997818</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>-0.1141699148043651</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-0.02018193834179483</v>
+        <v>-0.01680217193360389</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.2644058466600384</v>
+        <v>0.1681420033869722</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.2371394375531429</v>
+        <v>0.1460808548480409</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.4824853463797588</v>
+        <v>-0.8601142718612508</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.6964459305914494</v>
+        <v>-1.167661403801758</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>0.01858174605572593</v>
+        <v>-0.08654745008589283</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.2828979457913611</v>
+        <v>0.2167827378855797</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0.2177913835362562</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.1704318014677371</v>
+        <v>0.08288670619862404</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>-0.4846698697413376</v>
+        <v>-0.6181879083875443</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>24.37508070171511</v>
+        <v>17.44015561116002</v>
       </c>
     </row>
     <row r="5">
@@ -698,43 +698,43 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-0.1675001466446708</v>
+        <v>0.02130347599947102</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0.1298071537204202</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-0.2631487147041569</v>
+        <v>-0.09603734350915749</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.2556934050708824</v>
+        <v>0.2128900660123663</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1858033702302072</v>
+        <v>0.1324957764190179</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.6775705835729658</v>
+        <v>0.1370649015474772</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-0.9710298282053276</v>
+        <v>0.2421704446430386</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-1.674378803690923</v>
+        <v>-0.8202158746257192</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.2880552960546726</v>
+        <v>0.1897748252271627</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0.1515696200238076</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.3595363528113831</v>
+        <v>0.1769563685229771</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>-0.6032965124430565</v>
+        <v>0.1169464042591028</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>24.15625570542194</v>
+        <v>16.88601595217108</v>
       </c>
     </row>
     <row r="6">
@@ -744,43 +744,43 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.4291140192818952</v>
+        <v>0.2130431767090399</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0.2243203183030871</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.1672713406101523</v>
+        <v>-0.009210940491194308</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.3367816930684909</v>
+        <v>0.224884244817236</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.2545061826231909</v>
+        <v>0.1406875460262302</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.223842143577395</v>
+        <v>0.937173803004632</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.838991494497554</v>
+        <v>1.340355219596739</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.7978089507542897</v>
+        <v>0.01162366075679553</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.2142932324908138</v>
+        <v>0.1482330181190717</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0.1188658802983931</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.1822122712394958</v>
+        <v>0.1488502043612688</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.091239590895109</v>
+        <v>1.495963853507596</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>24.13090055135495</v>
+        <v>19.30828286168963</v>
       </c>
     </row>
     <row r="7">
@@ -790,43 +790,43 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.1934259834972012</v>
+        <v>0.1413954212976765</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>-0.01504143451691176</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.2116509519482852</v>
+        <v>0.1588258240465821</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.4829076461451166</v>
+        <v>0.2736733642853936</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.414601009011067</v>
+        <v>0.2078392585622412</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.8800316460900144</v>
+        <v>0.9650697561272387</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.248073962224466</v>
+        <v>1.349286330433473</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1.064391469902329</v>
+        <v>1.349300683264229</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.2647608768024196</v>
+        <v>0.1146770787932279</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0.127969093077366</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.2391055982632077</v>
+        <v>0.09049490277340144</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.439533567880863</v>
+        <v>2.382002597048261</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>23.96479285183576</v>
+        <v>19.00116835697887</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_r2/post_rank_positive_return_rsi_bias_filter/staggered_7d/rsi_7_gt_60__bias_15_gt_-0.02/next_day_vwap/next_day_vwap_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_r2/post_rank_positive_return_rsi_bias_filter/staggered_7d/rsi_7_gt_60__bias_15_gt_-0.02/next_day_vwap/next_day_vwap_annual_metrics.xlsx
@@ -477,7 +477,7 @@
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -560,43 +560,43 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.04019571119698995</v>
+        <v>0.01725737955790185</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>-0.02176047699359285</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.06333437438734091</v>
+        <v>0.03988579037532736</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.243585286192227</v>
+        <v>0.2714910255116372</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2133188844915984</v>
+        <v>0.2616856949435025</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.2429896634181241</v>
+        <v>0.151557227329887</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.3478406416891481</v>
+        <v>0.2178920475080968</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0.3881546535739639</v>
+        <v>0.2474664810800481</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1780505146516361</v>
+        <v>0.1663644031912246</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.1506490308477421</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1307537979417097</v>
+        <v>0.1870848680595399</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>0.2557718876385517</v>
+        <v>0.1173531527571886</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>18.67010033478667</v>
+        <v>19.88476220269606</v>
       </c>
     </row>
     <row r="3">
@@ -606,43 +606,43 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.1065702109520901</v>
+        <v>-0.1918833689475966</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>-0.2255774308756096</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.1536721999955126</v>
+        <v>0.04350862600260963</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.167508566734918</v>
+        <v>0.2122030090090785</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.1663819230219392</v>
+        <v>0.1958923052241979</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.7058908971028687</v>
+        <v>-1.009386548850004</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-0.9830068226522815</v>
+        <v>-1.359960128540788</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0.8476339579700458</v>
+        <v>0.2301207156648038</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.1495554488597143</v>
+        <v>0.2597074578095161</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>0.2845881262232945</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.09881169412402613</v>
+        <v>0.1438304641194263</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>-0.7403327986897263</v>
+        <v>-0.766117925344669</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>15.99836134352879</v>
+        <v>17.08473870229298</v>
       </c>
     </row>
     <row r="4">
@@ -652,43 +652,43 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.1290537841997818</v>
+        <v>-0.1174287401297196</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>-0.1141699148043651</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-0.01680217193360389</v>
+        <v>-0.003678837939484203</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.1681420033869722</v>
+        <v>0.1705774796418607</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.1460808548480409</v>
+        <v>0.1462477925617907</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.8601142718612508</v>
+        <v>-0.7646188673872909</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-1.167661403801758</v>
+        <v>-1.058570369050638</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.08654745008589283</v>
+        <v>0.01060974669288393</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.2167827378855797</v>
+        <v>0.2020689796625367</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0.2177913835362562</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.08288670619862404</v>
+        <v>0.06812440445491008</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>-0.6181879083875443</v>
+        <v>-0.603618951861002</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>17.44015561116002</v>
+        <v>16.1117259178968</v>
       </c>
     </row>
     <row r="5">
@@ -698,43 +698,43 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.02130347599947102</v>
+        <v>-0.07866841876536168</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0.1298071537204202</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-0.09603734350915749</v>
+        <v>-0.1845231478657919</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.2128900660123663</v>
+        <v>0.2170318508976913</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1324957764190179</v>
+        <v>0.160656494959784</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.1370649015474772</v>
+        <v>-0.3549862457363346</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.2421704446430386</v>
+        <v>-0.5497783635679602</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.8202158746257192</v>
+        <v>-1.337625454155045</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.1897748252271627</v>
+        <v>0.231674411319671</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0.1515696200238076</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.1769563685229771</v>
+        <v>0.2770935993998602</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0.1169464042591028</v>
+        <v>-0.3530063894659957</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>16.88601595217108</v>
+        <v>18.43371791986025</v>
       </c>
     </row>
     <row r="6">
@@ -744,43 +744,43 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.2130431767090399</v>
+        <v>0.06681811507091973</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0.2243203183030871</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>-0.009210940491194308</v>
+        <v>-0.1286446045839292</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.224884244817236</v>
+        <v>0.1819076756893954</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1406875460262302</v>
+        <v>0.1270216248862955</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.937173803004632</v>
+        <v>0.3780249480129101</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.340355219596739</v>
+        <v>0.5046274563527833</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.01162366075679553</v>
+        <v>-1.104966804852996</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.1482330181190717</v>
+        <v>0.1137231226638314</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0.1188658802983931</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.1488502043612688</v>
+        <v>0.2187970838594802</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>1.495963853507596</v>
+        <v>0.6100502570141353</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>19.30828286168963</v>
+        <v>18.56055183085562</v>
       </c>
     </row>
     <row r="7">
@@ -790,43 +790,43 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.1413954212976765</v>
+        <v>0.108288778386378</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>-0.01504143451691176</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.1588258240465821</v>
+        <v>0.1252136051457164</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.2736733642853936</v>
+        <v>0.2972344916479597</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.2078392585622412</v>
+        <v>0.2708144194284407</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.9650697561272387</v>
+        <v>0.7304039090218243</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.349286330433473</v>
+        <v>1.013006133317427</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1.349300683264229</v>
+        <v>0.8619371219086848</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1146770787932279</v>
+        <v>0.1441845211603905</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0.127969093077366</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.09049490277340144</v>
+        <v>0.1191354508084259</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>2.382002597048261</v>
+        <v>1.432439538049682</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>19.00116835697887</v>
+        <v>21.03642075731866</v>
       </c>
     </row>
   </sheetData>
